--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首汇 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3971,7 +3829,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -11857,2252 +11715,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>首汇 - 首汇 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>241 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>217 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 850呎 (4+房)
-$2,982万
-$35,082/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 415呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 408呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 274呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 265呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 347呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 348呎 (2房)
-$829万
-$23,819/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 356呎 (2房)
-$790万
-$22,181/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,377万
-$25,787/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,369万
-$25,774/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$1,002万
-$24,677/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$972万
-$23,817/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$639万
-$24,026/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$672万
-$24,520/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$574万
-$21,668/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$717万
-$20,653/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$730万
-$20,974/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$775万
-$21,773/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,630万
-$27,167/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,226万
-$22,952/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,310万
-$24,663/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$1,024万
-$25,215/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$961万
-$23,550/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$632万
-$23,755/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$664万
-$24,241/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$588万
-$22,204/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$710万
-$20,474/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$724万
-$20,793/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$773万
-$21,703/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,628万
-$27,133/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,219万
-$22,822/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,302万
-$24,522/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$1,018万
-$25,073/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$1,062万
-$26,020/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$628万
-$23,623/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$660万
-$24,103/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$568万
-$21,427/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$708万
-$20,417/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$722万
-$20,734/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$783万
-$21,996/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,207万
-$22,596/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,289万
-$24,276/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$975万
-$24,023/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$946万
-$23,184/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$622万
-$23,386/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$654万
-$23,857/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$563万
-$21,247/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$702万
-$20,238/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$739万
-$21,235/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$751万
-$21,099/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,200万
-$22,468/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,282万
-$24,136/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$921万
-$22,682/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$940万
-$23,051/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$639万
-$24,026/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$650万
-$23,715/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$560万
-$21,128/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$698万
-$20,119/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$790万
-$22,698/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$755万
-$21,206/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,249万
-$23,390/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,267万
-$23,856/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$910万
-$22,422/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$955万
-$23,398/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$611万
-$22,984/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$682万
-$24,885/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$557万
-$21,009/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$731万
-$21,063/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$779万
-$22,389/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$742万
-$20,849/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,236万
-$23,152/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,254万
-$23,610/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$901万
-$22,192/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$945万
-$23,157/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$605万
-$22,747/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$635万
-$23,193/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$554万
-$20,887/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$727万
-$20,939/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$721万
-$20,728/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$738万
-$20,725/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,585万
-$26,417/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,229万
-$23,017/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,179万
-$22,210/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$896万
-$22,061/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$939万
-$23,021/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$602万
-$22,632/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$671万
-$24,474/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$550万
-$20,768/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$722万
-$20,812/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$729万
-$20,948/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$733万
-$20,601/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,555万
-$25,912/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,236万
-$23,137/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,192万
-$22,446/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$890万
-$21,933/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$934万
-$22,884/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$600万
-$22,544/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$678万
-$24,731/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$549万
-$20,710/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$694万
-$20,005/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$715万
-$20,542/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$731万
-$20,538/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,257万
-$23,547/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,172万
-$22,078/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$938万
-$23,096/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$934万
-$22,884/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$600万
-$22,544/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$667万
-$24,326/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$589万
-$22,211/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$694万
-$20,005/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$715万
-$20,542/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$731万
-$20,538/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,551万
-$25,848/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,147万
-$21,472/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,158万
-$21,814/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$880万
-$21,671/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$908万
-$22,264/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$613万
-$23,035/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$658万
-$24,031/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$552万
-$20,832/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$686万
-$19,766/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$688万
-$19,761/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$722万
-$20,290/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,143万
-$21,408/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,155万
-$21,747/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$875万
-$21,540/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$893万
-$21,887/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$609万
-$22,892/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$616万
-$22,497/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$550万
-$20,769/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$684万
-$19,704/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$708万
-$20,358/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$725万
-$20,355/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,515万
-$25,250/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,136万
-$21,280/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,179万
-$22,195/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$867万
-$21,345/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$885万
-$21,686/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$624万
-$23,442/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$617万
-$22,534/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$531万
-$20,041/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$682万
-$19,644/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$706万
-$20,294/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$718万
-$20,179/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,176万
-$22,023/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,168万
-$21,992/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$851万
-$20,955/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$868万
-$21,287/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$592万
-$22,267/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$599万
-$21,869/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$529万
-$19,980/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$680万
-$19,608/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$681万
-$19,580/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$716万
-$20,119/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,123万
-$21,022/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,164万
-$21,922/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$845万
-$20,824/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$863万
-$21,154/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$589万
-$22,124/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$595万
-$21,728/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$528万
-$19,922/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$703万
-$20,246/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$679万
-$19,521/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$714万
-$20,055/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,119万
-$20,958/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,160万
-$21,854/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$840万
-$20,693/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$872万
-$21,372/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$604万
-$22,718/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$592万
-$21,590/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$532万
-$20,082/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$665万
-$19,170/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$677万
-$19,459/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$712万
-$19,995/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,488万
-$24,800/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,116万
-$20,894/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,163万
-$21,907/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$835万
-$20,563/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$852万
-$20,888/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$581万
-$21,847/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$591万
-$21,568/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$548万
-$20,683/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$663万
-$19,113/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$675万
-$19,399/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$717万
-$20,153/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,153万
-$21,590/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,157万
-$21,786/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$835万
-$20,563/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$852万
-$20,888/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$581万
-$21,847/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$597万
-$21,806/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$525万
-$19,803/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$663万
-$19,113/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$675万
-$19,399/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$710万
-$19,931/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1,478万
-$24,633/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,109万
-$20,766/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,183万
-$22,280/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$824万
-$20,303/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$869万
-$21,310/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$574万
-$21,566/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$580万
-$21,170/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$523万
-$19,746/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$659万
-$18,993/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$671万
-$19,278/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$705万
-$19,808/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1,105万
-$20,702/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1,179万
-$22,210/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$819万
-$20,172/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$836万
-$20,488/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$570万
-$21,424/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$576万
-$21,028/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$523万
-$19,729/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$655万
-$18,882/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$666万
-$19,148/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$701万
-$19,681/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 560呎 (4+房)
-$1,608万
-$28,714/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 498呎 (3房)
-$1,285万
-$25,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 493呎 (3房)
-$1,267万
-$25,700/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 369呎 (2房)
-$948万
-$25,700/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 370呎 (2房)
-$940万
-$25,400/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 229呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 236呎 (1房)
-$642万
-$27,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 228呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 309呎 (2房)
-$791万
-$25,600/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>K | 310呎 (2房)
-$784万
-$25,300/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>L | 319呎 (2房)
-$740万
-$23,200/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首汇" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +234,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -11715,4 +11911,2252 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>首汇 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 850呎 (4+房)
+$2982万
+$35,082/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 415呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 408呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 274呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 265呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 347呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 348呎 (2房)
+$829万
+$23,819/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 356呎 (2房)
+$790万
+$22,181/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1377万
+$25,787/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1369万
+$25,774/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$1002万
+$24,677/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$972万
+$23,817/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$639万
+$24,026/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$672万
+$24,520/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$574万
+$21,668/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$717万
+$20,653/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$730万
+$20,974/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$775万
+$21,773/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1630万
+$27,167/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1226万
+$22,952/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1310万
+$24,663/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$1024万
+$25,215/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$961万
+$23,550/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$632万
+$23,755/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$664万
+$24,241/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$588万
+$22,204/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$710万
+$20,474/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$724万
+$20,793/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$773万
+$21,703/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1628万
+$27,133/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1219万
+$22,822/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1302万
+$24,522/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$1018万
+$25,073/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$1062万
+$26,020/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$628万
+$23,623/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$660万
+$24,103/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$568万
+$21,427/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$708万
+$20,417/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$722万
+$20,734/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$783万
+$21,996/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1207万
+$22,596/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1289万
+$24,276/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$975万
+$24,023/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$946万
+$23,184/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$622万
+$23,386/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$654万
+$23,857/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$563万
+$21,247/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$702万
+$20,238/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$739万
+$21,235/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$751万
+$21,099/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1200万
+$22,468/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1282万
+$24,136/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$921万
+$22,682/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$940万
+$23,051/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$639万
+$24,026/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$650万
+$23,715/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$560万
+$21,128/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$698万
+$20,119/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$790万
+$22,698/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$755万
+$21,206/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1249万
+$23,390/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1267万
+$23,856/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$910万
+$22,422/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$955万
+$23,398/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$611万
+$22,984/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$682万
+$24,885/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$557万
+$21,009/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$731万
+$21,063/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$779万
+$22,389/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$742万
+$20,849/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1236万
+$23,152/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1254万
+$23,610/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$901万
+$22,192/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$945万
+$23,157/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$605万
+$22,747/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$635万
+$23,193/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$554万
+$20,887/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$727万
+$20,939/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$721万
+$20,728/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$738万
+$20,725/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1585万
+$26,417/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1229万
+$23,017/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1179万
+$22,210/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$896万
+$22,061/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$939万
+$23,021/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$602万
+$22,632/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$671万
+$24,474/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$550万
+$20,768/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$722万
+$20,812/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$729万
+$20,948/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$733万
+$20,601/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1555万
+$25,912/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1236万
+$23,137/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1192万
+$22,446/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$890万
+$21,933/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$934万
+$22,884/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$600万
+$22,544/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$678万
+$24,731/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$549万
+$20,710/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$694万
+$20,005/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$715万
+$20,542/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$731万
+$20,538/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1257万
+$23,547/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1172万
+$22,078/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$938万
+$23,096/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$934万
+$22,884/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$600万
+$22,544/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$667万
+$24,326/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$589万
+$22,211/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$694万
+$20,005/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$715万
+$20,542/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$731万
+$20,538/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1551万
+$25,848/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1147万
+$21,472/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1158万
+$21,814/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$880万
+$21,671/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$908万
+$22,264/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$613万
+$23,035/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$658万
+$24,031/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$552万
+$20,832/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$686万
+$19,766/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$688万
+$19,761/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$722万
+$20,290/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1143万
+$21,408/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1155万
+$21,747/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$875万
+$21,540/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$893万
+$21,887/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$609万
+$22,892/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$616万
+$22,497/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$550万
+$20,769/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$684万
+$19,704/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$708万
+$20,358/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$725万
+$20,355/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1515万
+$25,250/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1136万
+$21,280/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1179万
+$22,195/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$867万
+$21,345/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$885万
+$21,686/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$624万
+$23,442/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$617万
+$22,534/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$531万
+$20,041/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$682万
+$19,644/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$706万
+$20,294/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$718万
+$20,179/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1176万
+$22,023/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1168万
+$21,992/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$851万
+$20,955/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$868万
+$21,287/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$592万
+$22,267/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$599万
+$21,869/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$529万
+$19,980/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$680万
+$19,608/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$681万
+$19,580/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$716万
+$20,119/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1123万
+$21,022/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1164万
+$21,922/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$845万
+$20,824/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$863万
+$21,154/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$589万
+$22,124/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$595万
+$21,728/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$528万
+$19,922/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$703万
+$20,246/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$679万
+$19,521/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$714万
+$20,055/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1119万
+$20,958/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1160万
+$21,854/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$840万
+$20,693/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$872万
+$21,372/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$604万
+$22,718/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$592万
+$21,590/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$532万
+$20,082/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$665万
+$19,170/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$677万
+$19,459/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$712万
+$19,995/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1488万
+$24,800/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1116万
+$20,894/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1163万
+$21,907/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$835万
+$20,563/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$852万
+$20,888/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$581万
+$21,847/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$591万
+$21,568/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$548万
+$20,683/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$663万
+$19,113/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$675万
+$19,399/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$717万
+$20,153/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1153万
+$21,590/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1157万
+$21,786/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$835万
+$20,563/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$852万
+$20,888/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$581万
+$21,847/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$597万
+$21,806/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$525万
+$19,803/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$663万
+$19,113/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$675万
+$19,399/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$710万
+$19,931/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1478万
+$24,633/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1109万
+$20,766/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1183万
+$22,280/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$824万
+$20,303/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$869万
+$21,310/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$574万
+$21,566/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$580万
+$21,170/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$523万
+$19,746/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$659万
+$18,993/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$671万
+$19,278/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$705万
+$19,808/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1105万
+$20,702/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1179万
+$22,210/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$819万
+$20,172/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$836万
+$20,488/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$570万
+$21,424/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$576万
+$21,028/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$523万
+$19,729/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$655万
+$18,882/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$666万
+$19,148/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$701万
+$19,681/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 560呎 (4+房)
+$1608万
+$28,714/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 498呎 (3房)
+$1285万
+$25,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 493呎 (3房)
+$1267万
+$25,700/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 369呎 (2房)
+$948万
+$25,700/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 370呎 (2房)
+$940万
+$25,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 229呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 236呎 (1房)
+$642万
+$27,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 228呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 309呎 (2房)
+$791万
+$25,600/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 310呎 (2房)
+$784万
+$25,300/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>L | 319呎 (2房)
+$740万
+$23,200/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -670,7 +670,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -13308,7 +13308,7 @@
           <t>A | 600呎 (4+房)
 $1515万
 $25,250/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">

--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:N243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -730,6 +734,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -776,6 +800,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>7896600</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>22181</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -822,6 +862,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>8289000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>23819</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -872,6 +928,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -922,6 +998,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -972,6 +1068,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1022,6 +1138,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1072,6 +1208,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1122,6 +1278,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1172,6 +1348,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1218,6 +1414,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>29820000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>35082</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1264,6 +1476,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7751300</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21773</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1310,6 +1538,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7299000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>20974</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1356,6 +1600,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7166700</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20653</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1662,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5742000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>21668</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,6 +1724,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>6718500</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>24520</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1494,6 +1786,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6390900</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>24026</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1540,6 +1848,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>9717300</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>23817</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1586,6 +1910,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>10018800</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>24677</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1632,6 +1972,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>13685800</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>25774</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1678,6 +2034,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>12393000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>23208</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1728,6 +2100,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1774,6 +2166,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>7726200</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>21703</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1820,6 +2228,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>7236000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>20793</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1866,6 +2290,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>7104600</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>20474</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1912,6 +2352,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5884100</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>22204</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1958,6 +2414,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6642000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>24241</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2004,6 +2476,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>6318900</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>23755</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2050,6 +2538,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>9608400</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>23550</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2096,6 +2600,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10237400</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>25215</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2142,6 +2662,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>13095900</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>24663</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2188,6 +2724,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>12256200</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>22952</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2234,6 +2786,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>16300000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>27167</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2280,6 +2848,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>7830600</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>21996</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2326,6 +2910,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7215300</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>20734</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2372,6 +2972,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>7084800</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>20417</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2418,6 +3034,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5678100</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>21427</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2464,6 +3096,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6604200</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>24103</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2510,6 +3158,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6283800</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>23623</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2556,6 +3220,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9554400</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>23418</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2602,6 +3282,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>10179700</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>25073</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2648,6 +3344,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>13021200</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>24522</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2694,6 +3406,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>12186900</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22822</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2740,6 +3468,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>16280000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>27133</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2786,6 +3530,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>7511400</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>21099</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2832,6 +3592,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7389700</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>21235</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2878,6 +3654,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7022700</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>20238</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2924,6 +3716,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>5630400</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>21247</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2970,6 +3778,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6536700</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>23857</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3016,6 +3840,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6220800</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>23386</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3062,6 +3902,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>9459000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>23184</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3108,6 +3964,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>9753300</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>24023</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3154,6 +4026,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>12890700</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>24276</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3200,6 +4088,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>12066300</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>22596</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3250,6 +4154,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3296,6 +4220,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>7549300</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>21206</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3342,6 +4282,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7109100</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>20428</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3388,6 +4344,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6981300</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>20119</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3434,6 +4406,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5598900</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>21128</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3480,6 +4468,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>6498000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>23715</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3526,6 +4530,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6390900</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>24026</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3572,6 +4592,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>9405000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>23051</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3618,6 +4654,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>9208800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>22682</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3664,6 +4716,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>12816000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>24136</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3710,6 +4778,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>11997900</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22468</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3760,6 +4844,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3806,6 +4910,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7422300</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>20849</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3852,6 +4972,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>7791300</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>22389</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3898,6 +5034,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>7308900</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>21063</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3944,6 +5096,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>5567400</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>21009</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3990,6 +5158,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6818400</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>24885</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4036,6 +5220,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6113700</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>22984</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4082,6 +5282,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>9546300</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>23398</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4128,6 +5344,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>9103500</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>22422</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4174,6 +5406,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>12667500</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>23856</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4220,6 +5468,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>12490200</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>23390</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4270,6 +5534,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4316,6 +5600,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>7378200</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>20725</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4362,6 +5662,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>7213500</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>20728</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4408,6 +5724,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>7265700</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>20939</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4454,6 +5786,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>5535000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>20887</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4500,6 +5848,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>6354900</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>23193</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4546,6 +5910,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>6050700</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>22747</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4592,6 +5972,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>9448200</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>23157</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4638,6 +6034,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>9009900</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>22192</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4684,6 +6096,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>12537000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>23610</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4730,6 +6158,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>12363300</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>23152</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4780,6 +6224,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4826,6 +6290,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7334100</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>20601</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4872,6 +6352,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7289800</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20948</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4918,6 +6414,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>7221600</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>20812</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4964,6 +6476,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5503500</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>20768</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5010,6 +6538,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>6705900</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>24474</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5056,6 +6600,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>6020100</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>22632</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5102,6 +6662,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>9392400</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>23021</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5148,6 +6724,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8956800</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>22061</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5194,6 +6786,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>11793600</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>22210</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5240,6 +6848,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>12291300</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>23017</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5286,6 +6910,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>15850000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>26417</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5332,6 +6972,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7311600</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>20538</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5378,6 +7034,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>7148700</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5424,6 +7096,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>6941700</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>20005</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5470,6 +7158,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>5488200</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>20710</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5516,6 +7220,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>6776400</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>24731</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5562,6 +7282,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5996700</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>22544</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5608,6 +7344,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>9336600</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>22884</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5654,6 +7406,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>8904600</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>21933</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5700,6 +7468,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>11918700</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>22446</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5746,6 +7530,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>12355000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>23137</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5792,6 +7592,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>15547300</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>25912</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5838,6 +7654,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7311600</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>20538</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5884,6 +7716,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7148700</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5930,6 +7778,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>6941700</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>20005</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5976,6 +7840,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5886000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>22211</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6022,6 +7902,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>6665400</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>24326</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6068,6 +7964,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5996700</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>22544</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6114,6 +8026,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>9336600</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>22884</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6160,6 +8088,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>9377100</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>23096</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6206,6 +8150,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>11723400</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>22078</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6252,6 +8212,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>12573900</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>23547</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6302,6 +8278,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6348,6 +8344,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>7223400</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>20290</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6394,6 +8406,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>6876900</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>19761</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6440,6 +8468,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>6858900</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>19766</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6486,6 +8530,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>5520400</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>20832</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6532,6 +8592,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6584400</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>24031</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6578,6 +8654,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>6127200</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>23035</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6624,6 +8716,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>9083600</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>22264</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6670,6 +8778,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>8798400</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>21671</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6716,6 +8840,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>11583000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>21814</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6762,6 +8902,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>11466000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>21472</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6808,6 +8964,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>15509000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>25848</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6854,6 +9026,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>7246300</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>20355</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6900,6 +9088,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>7084700</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>20358</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6946,6 +9150,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>6837300</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>19704</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6992,6 +9212,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>5503700</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>20769</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7038,6 +9274,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>6164100</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>22497</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7084,6 +9336,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6089400</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>22892</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7130,6 +9398,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>8929800</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>21887</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7176,6 +9460,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>8745300</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>21540</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7222,6 +9522,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>11547900</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>21747</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7268,6 +9584,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>11431800</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>21408</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7318,6 +9650,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7364,6 +9716,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>7183800</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>20179</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7410,6 +9778,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>7062400</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>20294</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7456,6 +9840,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>6816600</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>19644</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7502,6 +9902,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5310900</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>20041</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7548,6 +9964,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6174300</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>22534</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7594,6 +10026,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6235600</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>23442</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7640,6 +10088,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>8847900</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>21686</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7686,6 +10150,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>8666100</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>21345</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7732,6 +10212,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>11785500</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>22195</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7778,6 +10274,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>11363400</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21280</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7824,6 +10336,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>15150000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>25250</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7870,6 +10398,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>7162200</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>20119</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7916,6 +10460,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>6813900</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>19580</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7962,6 +10522,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6804000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>19608</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8008,6 +10584,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>5294700</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>19980</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8054,6 +10646,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>5992200</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>21869</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8100,6 +10708,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>5922900</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>22267</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8146,6 +10770,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>8685000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21287</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8192,6 +10832,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>8507700</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>20955</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8238,6 +10894,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>11677500</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>21992</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8284,6 +10956,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>11760300</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>22023</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8334,6 +11022,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8380,6 +11088,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>7139700</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>20055</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8426,6 +11150,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>6793200</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>19521</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8472,6 +11212,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>7025400</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>20246</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8518,6 +11274,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>5279400</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>19922</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8564,6 +11336,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>5953500</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>21728</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8610,6 +11398,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>5885100</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>22124</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8656,6 +11460,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>8631000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>21154</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8702,6 +11522,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>8454600</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>20824</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8748,6 +11584,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>11640600</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>21922</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8794,6 +11646,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>11225700</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>21022</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8844,6 +11712,26 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8890,6 +11778,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>7118100</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>19995</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8936,6 +11840,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>6771600</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>19459</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8982,6 +11902,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>6651900</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>19170</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9028,6 +11964,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>5321600</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>20082</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9074,6 +12026,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>5915700</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>21590</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9120,6 +12088,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>6043100</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>22718</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9166,6 +12150,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>8719900</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>21372</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9212,6 +12212,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>8401500</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>20693</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9258,6 +12274,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>11604600</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>21854</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9304,6 +12336,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>11191500</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>20958</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9354,6 +12402,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9400,6 +12468,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>7174400</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>20153</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9446,6 +12530,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>6750900</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>19399</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9492,6 +12592,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>6632100</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>19113</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9538,6 +12654,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>5481100</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>20683</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9584,6 +12716,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>5909600</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>21568</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9630,6 +12778,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>5811300</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>21847</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9676,6 +12840,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>8522100</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>20888</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9722,6 +12902,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>8348400</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>20563</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9768,6 +12964,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>11632800</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>21907</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9814,6 +13026,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>11157300</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>20894</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9860,6 +13088,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>14880000</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>24800</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9906,6 +13150,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>7095600</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>19931</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9952,6 +13212,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>6750900</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>19399</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9998,6 +13274,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>6632100</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>19113</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10044,6 +13336,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>5247900</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>19803</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10090,6 +13398,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>5974900</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>21806</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10136,6 +13460,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>5811300</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21847</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10182,6 +13522,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>8522100</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>20888</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10228,6 +13584,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>8348400</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>20563</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10274,6 +13646,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>11568600</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>21786</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10320,6 +13708,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>11529200</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>21590</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10370,6 +13774,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10416,6 +13840,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>7051500</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>19808</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10462,6 +13902,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>6708600</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>19278</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10508,6 +13964,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>6590700</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>18993</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10554,6 +14026,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>5232600</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>19746</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10600,6 +14088,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>5800500</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>21170</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10646,6 +14150,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>5736600</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>21566</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10692,6 +14212,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>8694500</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>21310</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10738,6 +14274,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>8243100</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>20303</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10784,6 +14336,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>11830500</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>22280</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10830,6 +14398,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>11088900</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>20766</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10876,6 +14460,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>14780000</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>24633</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10922,6 +14522,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>7006500</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>19681</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10968,6 +14584,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>6663600</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>19148</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11014,6 +14646,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>6552000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>18882</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11060,6 +14708,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>5228100</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>19729</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11106,6 +14770,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>5761800</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>21028</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11152,6 +14832,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>5698800</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>21424</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11198,6 +14894,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>8359200</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>20488</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11244,6 +14956,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>8190000</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>20172</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11290,6 +15018,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>11793600</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>22210</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11336,6 +15080,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>11054700</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>20702</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11386,6 +15146,26 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11432,6 +15212,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7400800</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>23200</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11478,6 +15274,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>7843000</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>25300</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11524,6 +15336,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>7910400</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>25600</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11574,6 +15402,26 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11620,6 +15468,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>6419200</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>27200</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11670,6 +15534,26 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11716,6 +15600,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>9398000</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>25400</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11762,6 +15662,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>9483300</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>25700</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11808,6 +15724,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>12670000</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>25700</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11854,6 +15786,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>12848400</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>25800</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11900,13 +15848,29 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>16080000</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>28714</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -12080,7 +16044,7 @@
           <t>A | 850呎 (4+房)
 $2982万
 $35,082/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -12144,7 +16108,7 @@
           <t>J | 348呎 (2房)
 $829万
 $23,819/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -12152,7 +16116,7 @@
           <t>K | 356呎 (2房)
 $790万
 $22,181/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr"/>
@@ -12184,7 +16148,7 @@
           <t>C | 531呎 (3房)
 $1369万
 $25,774/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -12192,7 +16156,7 @@
           <t>D | 406呎 (2房)
 $1002万
 $24,677/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -12200,7 +16164,7 @@
           <t>E | 408呎 (2房)
 $972万
 $23,817/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -12208,7 +16172,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -12216,7 +16180,7 @@
           <t>G | 274呎 (1房)
 $672万
 $24,520/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -12224,7 +16188,7 @@
           <t>H | 265呎 (1房)
 $574万
 $21,668/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -12232,7 +16196,7 @@
           <t>J | 347呎 (2房)
 $717万
 $20,653/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -12240,7 +16204,7 @@
           <t>K | 348呎 (2房)
 $730万
 $20,974/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -12248,7 +16212,7 @@
           <t>L | 356呎 (2房)
 $775万
 $21,773/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -12263,7 +16227,7 @@
           <t>A | 600呎 (4+房)
 $1630万
 $27,167/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12271,7 +16235,7 @@
           <t>B | 534呎 (3房)
 $1226万
 $22,952/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -12279,7 +16243,7 @@
           <t>C | 531呎 (3房)
 $1310万
 $24,663/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -12287,7 +16251,7 @@
           <t>D | 406呎 (2房)
 $1024万
 $25,215/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -12295,7 +16259,7 @@
           <t>E | 408呎 (2房)
 $961万
 $23,550/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -12303,7 +16267,7 @@
           <t>F | 266呎 (1房)
 $632万
 $23,755/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -12311,7 +16275,7 @@
           <t>G | 274呎 (1房)
 $664万
 $24,241/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -12319,7 +16283,7 @@
           <t>H | 265呎 (1房)
 $588万
 $22,204/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -12327,7 +16291,7 @@
           <t>J | 347呎 (2房)
 $710万
 $20,474/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -12335,7 +16299,7 @@
           <t>K | 348呎 (2房)
 $724万
 $20,793/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -12343,7 +16307,7 @@
           <t>L | 356呎 (2房)
 $773万
 $21,703/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -12358,7 +16322,7 @@
           <t>A | 600呎 (4+房)
 $1628万
 $27,133/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -12366,7 +16330,7 @@
           <t>B | 534呎 (3房)
 $1219万
 $22,822/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -12374,7 +16338,7 @@
           <t>C | 531呎 (3房)
 $1302万
 $24,522/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -12382,7 +16346,7 @@
           <t>D | 406呎 (2房)
 $1018万
 $25,073/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -12398,7 +16362,7 @@
           <t>F | 266呎 (1房)
 $628万
 $23,623/呎
-(26年-03月)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -12406,7 +16370,7 @@
           <t>G | 274呎 (1房)
 $660万
 $24,103/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -12414,7 +16378,7 @@
           <t>H | 265呎 (1房)
 $568万
 $21,427/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -12422,7 +16386,7 @@
           <t>J | 347呎 (2房)
 $708万
 $20,417/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -12430,7 +16394,7 @@
           <t>K | 348呎 (2房)
 $722万
 $20,734/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -12438,7 +16402,7 @@
           <t>L | 356呎 (2房)
 $783万
 $21,996/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -12461,7 +16425,7 @@
           <t>B | 534呎 (3房)
 $1207万
 $22,596/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -12469,7 +16433,7 @@
           <t>C | 531呎 (3房)
 $1289万
 $24,276/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -12477,7 +16441,7 @@
           <t>D | 406呎 (2房)
 $975万
 $24,023/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -12485,7 +16449,7 @@
           <t>E | 408呎 (2房)
 $946万
 $23,184/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -12493,7 +16457,7 @@
           <t>F | 266呎 (1房)
 $622万
 $23,386/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -12501,7 +16465,7 @@
           <t>G | 274呎 (1房)
 $654万
 $23,857/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -12509,7 +16473,7 @@
           <t>H | 265呎 (1房)
 $563万
 $21,247/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -12517,7 +16481,7 @@
           <t>J | 347呎 (2房)
 $702万
 $20,238/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -12525,7 +16489,7 @@
           <t>K | 348呎 (2房)
 $739万
 $21,235/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -12533,7 +16497,7 @@
           <t>L | 356呎 (2房)
 $751万
 $21,099/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -12556,7 +16520,7 @@
           <t>B | 534呎 (3房)
 $1200万
 $22,468/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -12564,7 +16528,7 @@
           <t>C | 531呎 (3房)
 $1282万
 $24,136/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -12572,7 +16536,7 @@
           <t>D | 406呎 (2房)
 $921万
 $22,682/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -12580,7 +16544,7 @@
           <t>E | 408呎 (2房)
 $940万
 $23,051/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -12588,7 +16552,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -12596,7 +16560,7 @@
           <t>G | 274呎 (1房)
 $650万
 $23,715/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -12604,7 +16568,7 @@
           <t>H | 265呎 (1房)
 $560万
 $21,128/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -12612,7 +16576,7 @@
           <t>J | 347呎 (2房)
 $698万
 $20,119/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
@@ -12628,7 +16592,7 @@
           <t>L | 356呎 (2房)
 $755万
 $21,206/呎
-(26年-04月)</t>
+(26年-04月-06日)</t>
         </is>
       </c>
     </row>
@@ -12651,7 +16615,7 @@
           <t>B | 534呎 (3房)
 $1249万
 $23,390/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -12659,7 +16623,7 @@
           <t>C | 531呎 (3房)
 $1267万
 $23,856/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -12667,7 +16631,7 @@
           <t>D | 406呎 (2房)
 $910万
 $22,422/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -12675,7 +16639,7 @@
           <t>E | 408呎 (2房)
 $955万
 $23,398/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -12683,7 +16647,7 @@
           <t>F | 266呎 (1房)
 $611万
 $22,984/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -12691,7 +16655,7 @@
           <t>G | 274呎 (1房)
 $682万
 $24,885/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -12699,7 +16663,7 @@
           <t>H | 265呎 (1房)
 $557万
 $21,009/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -12707,7 +16671,7 @@
           <t>J | 347呎 (2房)
 $731万
 $21,063/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -12715,7 +16679,7 @@
           <t>K | 348呎 (2房)
 $779万
 $22,389/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -12723,7 +16687,7 @@
           <t>L | 356呎 (2房)
 $742万
 $20,849/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -12746,7 +16710,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,152/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -12754,7 +16718,7 @@
           <t>C | 531呎 (3房)
 $1254万
 $23,610/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -12762,7 +16726,7 @@
           <t>D | 406呎 (2房)
 $901万
 $22,192/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -12770,7 +16734,7 @@
           <t>E | 408呎 (2房)
 $945万
 $23,157/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -12778,7 +16742,7 @@
           <t>F | 266呎 (1房)
 $605万
 $22,747/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -12786,7 +16750,7 @@
           <t>G | 274呎 (1房)
 $635万
 $23,193/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -12794,7 +16758,7 @@
           <t>H | 265呎 (1房)
 $554万
 $20,887/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -12802,7 +16766,7 @@
           <t>J | 347呎 (2房)
 $727万
 $20,939/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -12810,7 +16774,7 @@
           <t>K | 348呎 (2房)
 $721万
 $20,728/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -12818,7 +16782,7 @@
           <t>L | 356呎 (2房)
 $738万
 $20,725/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -12833,7 +16797,7 @@
           <t>A | 600呎 (4+房)
 $1585万
 $26,417/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -12841,7 +16805,7 @@
           <t>B | 534呎 (3房)
 $1229万
 $23,017/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -12849,7 +16813,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-03月)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -12857,7 +16821,7 @@
           <t>D | 406呎 (2房)
 $896万
 $22,061/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -12865,7 +16829,7 @@
           <t>E | 408呎 (2房)
 $939万
 $23,021/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -12873,7 +16837,7 @@
           <t>F | 266呎 (1房)
 $602万
 $22,632/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -12881,7 +16845,7 @@
           <t>G | 274呎 (1房)
 $671万
 $24,474/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -12889,7 +16853,7 @@
           <t>H | 265呎 (1房)
 $550万
 $20,768/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -12897,7 +16861,7 @@
           <t>J | 347呎 (2房)
 $722万
 $20,812/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -12905,7 +16869,7 @@
           <t>K | 348呎 (2房)
 $729万
 $20,948/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -12913,7 +16877,7 @@
           <t>L | 356呎 (2房)
 $733万
 $20,601/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -12928,7 +16892,7 @@
           <t>A | 600呎 (4+房)
 $1555万
 $25,912/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12936,7 +16900,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,137/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12944,7 +16908,7 @@
           <t>C | 531呎 (3房)
 $1192万
 $22,446/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -12952,7 +16916,7 @@
           <t>D | 406呎 (2房)
 $890万
 $21,933/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -12960,7 +16924,7 @@
           <t>E | 408呎 (2房)
 $934万
 $22,884/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -12968,7 +16932,7 @@
           <t>F | 266呎 (1房)
 $600万
 $22,544/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -12976,7 +16940,7 @@
           <t>G | 274呎 (1房)
 $678万
 $24,731/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -12984,7 +16948,7 @@
           <t>H | 265呎 (1房)
 $549万
 $20,710/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -12992,7 +16956,7 @@
           <t>J | 347呎 (2房)
 $694万
 $20,005/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -13000,7 +16964,7 @@
           <t>K | 348呎 (2房)
 $715万
 $20,542/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -13008,7 +16972,7 @@
           <t>L | 356呎 (2房)
 $731万
 $20,538/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -13031,7 +16995,7 @@
           <t>B | 534呎 (3房)
 $1257万
 $23,547/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -13039,7 +17003,7 @@
           <t>C | 531呎 (3房)
 $1172万
 $22,078/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -13047,7 +17011,7 @@
           <t>D | 406呎 (2房)
 $938万
 $23,096/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -13055,7 +17019,7 @@
           <t>E | 408呎 (2房)
 $934万
 $22,884/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -13063,7 +17027,7 @@
           <t>F | 266呎 (1房)
 $600万
 $22,544/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -13071,7 +17035,7 @@
           <t>G | 274呎 (1房)
 $667万
 $24,326/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -13079,7 +17043,7 @@
           <t>H | 265呎 (1房)
 $589万
 $22,211/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -13087,7 +17051,7 @@
           <t>J | 347呎 (2房)
 $694万
 $20,005/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -13095,7 +17059,7 @@
           <t>K | 348呎 (2房)
 $715万
 $20,542/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -13103,7 +17067,7 @@
           <t>L | 356呎 (2房)
 $731万
 $20,538/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -13118,7 +17082,7 @@
           <t>A | 600呎 (4+房)
 $1551万
 $25,848/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -13126,7 +17090,7 @@
           <t>B | 534呎 (3房)
 $1147万
 $21,472/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -13134,7 +17098,7 @@
           <t>C | 531呎 (3房)
 $1158万
 $21,814/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -13142,7 +17106,7 @@
           <t>D | 406呎 (2房)
 $880万
 $21,671/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -13150,7 +17114,7 @@
           <t>E | 408呎 (2房)
 $908万
 $22,264/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -13158,7 +17122,7 @@
           <t>F | 266呎 (1房)
 $613万
 $23,035/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -13166,7 +17130,7 @@
           <t>G | 274呎 (1房)
 $658万
 $24,031/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -13174,7 +17138,7 @@
           <t>H | 265呎 (1房)
 $552万
 $20,832/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -13182,7 +17146,7 @@
           <t>J | 347呎 (2房)
 $686万
 $19,766/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -13190,7 +17154,7 @@
           <t>K | 348呎 (2房)
 $688万
 $19,761/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -13198,7 +17162,7 @@
           <t>L | 356呎 (2房)
 $722万
 $20,290/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -13221,7 +17185,7 @@
           <t>B | 534呎 (3房)
 $1143万
 $21,408/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -13229,7 +17193,7 @@
           <t>C | 531呎 (3房)
 $1155万
 $21,747/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -13237,7 +17201,7 @@
           <t>D | 406呎 (2房)
 $875万
 $21,540/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -13245,7 +17209,7 @@
           <t>E | 408呎 (2房)
 $893万
 $21,887/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -13253,7 +17217,7 @@
           <t>F | 266呎 (1房)
 $609万
 $22,892/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -13261,7 +17225,7 @@
           <t>G | 274呎 (1房)
 $616万
 $22,497/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -13269,7 +17233,7 @@
           <t>H | 265呎 (1房)
 $550万
 $20,769/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -13277,7 +17241,7 @@
           <t>J | 347呎 (2房)
 $684万
 $19,704/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -13285,7 +17249,7 @@
           <t>K | 348呎 (2房)
 $708万
 $20,358/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -13293,7 +17257,7 @@
           <t>L | 356呎 (2房)
 $725万
 $20,355/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -13308,7 +17272,7 @@
           <t>A | 600呎 (4+房)
 $1515万
 $25,250/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -13316,7 +17280,7 @@
           <t>B | 534呎 (3房)
 $1136万
 $21,280/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -13324,7 +17288,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,195/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -13332,7 +17296,7 @@
           <t>D | 406呎 (2房)
 $867万
 $21,345/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -13340,7 +17304,7 @@
           <t>E | 408呎 (2房)
 $885万
 $21,686/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -13348,7 +17312,7 @@
           <t>F | 266呎 (1房)
 $624万
 $23,442/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -13356,7 +17320,7 @@
           <t>G | 274呎 (1房)
 $617万
 $22,534/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -13364,7 +17328,7 @@
           <t>H | 265呎 (1房)
 $531万
 $20,041/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -13372,7 +17336,7 @@
           <t>J | 347呎 (2房)
 $682万
 $19,644/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -13380,7 +17344,7 @@
           <t>K | 348呎 (2房)
 $706万
 $20,294/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -13388,7 +17352,7 @@
           <t>L | 356呎 (2房)
 $718万
 $20,179/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -13411,7 +17375,7 @@
           <t>B | 534呎 (3房)
 $1176万
 $22,023/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -13419,7 +17383,7 @@
           <t>C | 531呎 (3房)
 $1168万
 $21,992/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -13427,7 +17391,7 @@
           <t>D | 406呎 (2房)
 $851万
 $20,955/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -13435,7 +17399,7 @@
           <t>E | 408呎 (2房)
 $868万
 $21,287/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -13443,7 +17407,7 @@
           <t>F | 266呎 (1房)
 $592万
 $22,267/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -13451,7 +17415,7 @@
           <t>G | 274呎 (1房)
 $599万
 $21,869/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -13459,7 +17423,7 @@
           <t>H | 265呎 (1房)
 $529万
 $19,980/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -13467,7 +17431,7 @@
           <t>J | 347呎 (2房)
 $680万
 $19,608/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -13475,7 +17439,7 @@
           <t>K | 348呎 (2房)
 $681万
 $19,580/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -13483,7 +17447,7 @@
           <t>L | 356呎 (2房)
 $716万
 $20,119/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -13506,7 +17470,7 @@
           <t>B | 534呎 (3房)
 $1123万
 $21,022/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -13514,7 +17478,7 @@
           <t>C | 531呎 (3房)
 $1164万
 $21,922/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -13522,7 +17486,7 @@
           <t>D | 406呎 (2房)
 $845万
 $20,824/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -13530,7 +17494,7 @@
           <t>E | 408呎 (2房)
 $863万
 $21,154/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -13538,7 +17502,7 @@
           <t>F | 266呎 (1房)
 $589万
 $22,124/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -13546,7 +17510,7 @@
           <t>G | 274呎 (1房)
 $595万
 $21,728/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -13554,7 +17518,7 @@
           <t>H | 265呎 (1房)
 $528万
 $19,922/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -13562,7 +17526,7 @@
           <t>J | 347呎 (2房)
 $703万
 $20,246/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -13570,7 +17534,7 @@
           <t>K | 348呎 (2房)
 $679万
 $19,521/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -13578,7 +17542,7 @@
           <t>L | 356呎 (2房)
 $714万
 $20,055/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -13601,7 +17565,7 @@
           <t>B | 534呎 (3房)
 $1119万
 $20,958/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -13609,7 +17573,7 @@
           <t>C | 531呎 (3房)
 $1160万
 $21,854/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -13617,7 +17581,7 @@
           <t>D | 406呎 (2房)
 $840万
 $20,693/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -13625,7 +17589,7 @@
           <t>E | 408呎 (2房)
 $872万
 $21,372/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -13633,7 +17597,7 @@
           <t>F | 266呎 (1房)
 $604万
 $22,718/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -13641,7 +17605,7 @@
           <t>G | 274呎 (1房)
 $592万
 $21,590/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -13649,7 +17613,7 @@
           <t>H | 265呎 (1房)
 $532万
 $20,082/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -13657,7 +17621,7 @@
           <t>J | 347呎 (2房)
 $665万
 $19,170/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -13665,7 +17629,7 @@
           <t>K | 348呎 (2房)
 $677万
 $19,459/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -13673,7 +17637,7 @@
           <t>L | 356呎 (2房)
 $712万
 $19,995/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -13688,7 +17652,7 @@
           <t>A | 600呎 (4+房)
 $1488万
 $24,800/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13696,7 +17660,7 @@
           <t>B | 534呎 (3房)
 $1116万
 $20,894/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -13704,7 +17668,7 @@
           <t>C | 531呎 (3房)
 $1163万
 $21,907/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -13712,7 +17676,7 @@
           <t>D | 406呎 (2房)
 $835万
 $20,563/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -13720,7 +17684,7 @@
           <t>E | 408呎 (2房)
 $852万
 $20,888/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -13728,7 +17692,7 @@
           <t>F | 266呎 (1房)
 $581万
 $21,847/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -13736,7 +17700,7 @@
           <t>G | 274呎 (1房)
 $591万
 $21,568/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -13744,7 +17708,7 @@
           <t>H | 265呎 (1房)
 $548万
 $20,683/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -13752,7 +17716,7 @@
           <t>J | 347呎 (2房)
 $663万
 $19,113/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -13760,7 +17724,7 @@
           <t>K | 348呎 (2房)
 $675万
 $19,399/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -13768,7 +17732,7 @@
           <t>L | 356呎 (2房)
 $717万
 $20,153/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -13791,7 +17755,7 @@
           <t>B | 534呎 (3房)
 $1153万
 $21,590/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -13799,7 +17763,7 @@
           <t>C | 531呎 (3房)
 $1157万
 $21,786/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -13807,7 +17771,7 @@
           <t>D | 406呎 (2房)
 $835万
 $20,563/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -13815,7 +17779,7 @@
           <t>E | 408呎 (2房)
 $852万
 $20,888/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -13823,7 +17787,7 @@
           <t>F | 266呎 (1房)
 $581万
 $21,847/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -13831,7 +17795,7 @@
           <t>G | 274呎 (1房)
 $597万
 $21,806/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -13839,7 +17803,7 @@
           <t>H | 265呎 (1房)
 $525万
 $19,803/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -13847,7 +17811,7 @@
           <t>J | 347呎 (2房)
 $663万
 $19,113/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -13855,7 +17819,7 @@
           <t>K | 348呎 (2房)
 $675万
 $19,399/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -13863,7 +17827,7 @@
           <t>L | 356呎 (2房)
 $710万
 $19,931/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -13878,7 +17842,7 @@
           <t>A | 600呎 (4+房)
 $1478万
 $24,633/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13886,7 +17850,7 @@
           <t>B | 534呎 (3房)
 $1109万
 $20,766/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13894,7 +17858,7 @@
           <t>C | 531呎 (3房)
 $1183万
 $22,280/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -13902,7 +17866,7 @@
           <t>D | 406呎 (2房)
 $824万
 $20,303/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -13910,7 +17874,7 @@
           <t>E | 408呎 (2房)
 $869万
 $21,310/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -13918,7 +17882,7 @@
           <t>F | 266呎 (1房)
 $574万
 $21,566/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -13926,7 +17890,7 @@
           <t>G | 274呎 (1房)
 $580万
 $21,170/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -13934,7 +17898,7 @@
           <t>H | 265呎 (1房)
 $523万
 $19,746/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -13942,7 +17906,7 @@
           <t>J | 347呎 (2房)
 $659万
 $18,993/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -13950,7 +17914,7 @@
           <t>K | 348呎 (2房)
 $671万
 $19,278/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -13958,7 +17922,7 @@
           <t>L | 356呎 (2房)
 $705万
 $19,808/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -13981,7 +17945,7 @@
           <t>B | 534呎 (3房)
 $1105万
 $20,702/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -13989,7 +17953,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -13997,7 +17961,7 @@
           <t>D | 406呎 (2房)
 $819万
 $20,172/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -14005,7 +17969,7 @@
           <t>E | 408呎 (2房)
 $836万
 $20,488/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -14013,7 +17977,7 @@
           <t>F | 266呎 (1房)
 $570万
 $21,424/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -14021,7 +17985,7 @@
           <t>G | 274呎 (1房)
 $576万
 $21,028/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -14029,7 +17993,7 @@
           <t>H | 265呎 (1房)
 $523万
 $19,729/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -14037,7 +18001,7 @@
           <t>J | 347呎 (2房)
 $655万
 $18,882/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -14045,7 +18009,7 @@
           <t>K | 348呎 (2房)
 $666万
 $19,148/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -14053,7 +18017,7 @@
           <t>L | 356呎 (2房)
 $701万
 $19,681/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -14068,7 +18032,7 @@
           <t>A | 560呎 (4+房)
 $1608万
 $28,714/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -14076,7 +18040,7 @@
           <t>B | 498呎 (3房)
 $1285万
 $25,800/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -14084,7 +18048,7 @@
           <t>C | 493呎 (3房)
 $1267万
 $25,700/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -14092,7 +18056,7 @@
           <t>D | 369呎 (2房)
 $948万
 $25,700/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -14100,7 +18064,7 @@
           <t>E | 370呎 (2房)
 $940万
 $25,400/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -14116,7 +18080,7 @@
           <t>G | 236呎 (1房)
 $642万
 $27,200/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -14132,7 +18096,7 @@
           <t>J | 309呎 (2房)
 $791万
 $25,600/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -14140,7 +18104,7 @@
           <t>K | 310呎 (2房)
 $784万
 $25,300/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -14148,7 +18112,7 @@
           <t>L | 319呎 (2房)
 $740万
 $23,200/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -16044,7 +16044,7 @@
           <t>A | 850呎 (4+房)
 $2982万
 $35,082/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -16108,7 +16108,7 @@
           <t>J | 348呎 (2房)
 $829万
 $23,819/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -16116,7 +16116,7 @@
           <t>K | 356呎 (2房)
 $790万
 $22,181/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr"/>
@@ -16148,7 +16148,7 @@
           <t>C | 531呎 (3房)
 $1369万
 $25,774/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -16156,7 +16156,7 @@
           <t>D | 406呎 (2房)
 $1002万
 $24,677/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -16164,7 +16164,7 @@
           <t>E | 408呎 (2房)
 $972万
 $23,817/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -16172,7 +16172,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -16180,7 +16180,7 @@
           <t>G | 274呎 (1房)
 $672万
 $24,520/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -16188,7 +16188,7 @@
           <t>H | 265呎 (1房)
 $574万
 $21,668/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -16196,7 +16196,7 @@
           <t>J | 347呎 (2房)
 $717万
 $20,653/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -16204,7 +16204,7 @@
           <t>K | 348呎 (2房)
 $730万
 $20,974/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -16212,7 +16212,7 @@
           <t>L | 356呎 (2房)
 $775万
 $21,773/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
           <t>A | 600呎 (4+房)
 $1630万
 $27,167/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -16235,7 +16235,7 @@
           <t>B | 534呎 (3房)
 $1226万
 $22,952/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -16243,7 +16243,7 @@
           <t>C | 531呎 (3房)
 $1310万
 $24,663/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -16251,7 +16251,7 @@
           <t>D | 406呎 (2房)
 $1024万
 $25,215/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -16259,7 +16259,7 @@
           <t>E | 408呎 (2房)
 $961万
 $23,550/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -16267,7 +16267,7 @@
           <t>F | 266呎 (1房)
 $632万
 $23,755/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -16275,7 +16275,7 @@
           <t>G | 274呎 (1房)
 $664万
 $24,241/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -16283,7 +16283,7 @@
           <t>H | 265呎 (1房)
 $588万
 $22,204/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -16291,7 +16291,7 @@
           <t>J | 347呎 (2房)
 $710万
 $20,474/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -16299,7 +16299,7 @@
           <t>K | 348呎 (2房)
 $724万
 $20,793/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -16307,7 +16307,7 @@
           <t>L | 356呎 (2房)
 $773万
 $21,703/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
           <t>A | 600呎 (4+房)
 $1628万
 $27,133/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -16330,7 +16330,7 @@
           <t>B | 534呎 (3房)
 $1219万
 $22,822/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -16338,7 +16338,7 @@
           <t>C | 531呎 (3房)
 $1302万
 $24,522/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -16346,7 +16346,7 @@
           <t>D | 406呎 (2房)
 $1018万
 $25,073/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -16362,7 +16362,7 @@
           <t>F | 266呎 (1房)
 $628万
 $23,623/呎
-(26年-03月-27日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -16370,7 +16370,7 @@
           <t>G | 274呎 (1房)
 $660万
 $24,103/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -16378,7 +16378,7 @@
           <t>H | 265呎 (1房)
 $568万
 $21,427/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -16386,7 +16386,7 @@
           <t>J | 347呎 (2房)
 $708万
 $20,417/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -16394,7 +16394,7 @@
           <t>K | 348呎 (2房)
 $722万
 $20,734/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -16402,7 +16402,7 @@
           <t>L | 356呎 (2房)
 $783万
 $21,996/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
           <t>B | 534呎 (3房)
 $1207万
 $22,596/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -16433,7 +16433,7 @@
           <t>C | 531呎 (3房)
 $1289万
 $24,276/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -16441,7 +16441,7 @@
           <t>D | 406呎 (2房)
 $975万
 $24,023/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -16449,7 +16449,7 @@
           <t>E | 408呎 (2房)
 $946万
 $23,184/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -16457,7 +16457,7 @@
           <t>F | 266呎 (1房)
 $622万
 $23,386/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -16465,7 +16465,7 @@
           <t>G | 274呎 (1房)
 $654万
 $23,857/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -16473,7 +16473,7 @@
           <t>H | 265呎 (1房)
 $563万
 $21,247/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -16481,7 +16481,7 @@
           <t>J | 347呎 (2房)
 $702万
 $20,238/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -16489,7 +16489,7 @@
           <t>K | 348呎 (2房)
 $739万
 $21,235/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -16497,7 +16497,7 @@
           <t>L | 356呎 (2房)
 $751万
 $21,099/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
           <t>B | 534呎 (3房)
 $1200万
 $22,468/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -16528,7 +16528,7 @@
           <t>C | 531呎 (3房)
 $1282万
 $24,136/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -16536,7 +16536,7 @@
           <t>D | 406呎 (2房)
 $921万
 $22,682/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -16544,7 +16544,7 @@
           <t>E | 408呎 (2房)
 $940万
 $23,051/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -16552,7 +16552,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -16560,7 +16560,7 @@
           <t>G | 274呎 (1房)
 $650万
 $23,715/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -16568,7 +16568,7 @@
           <t>H | 265呎 (1房)
 $560万
 $21,128/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -16576,7 +16576,7 @@
           <t>J | 347呎 (2房)
 $698万
 $20,119/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
@@ -16592,7 +16592,7 @@
           <t>L | 356呎 (2房)
 $755万
 $21,206/呎
-(26年-04月-06日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16615,7 @@
           <t>B | 534呎 (3房)
 $1249万
 $23,390/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -16623,7 +16623,7 @@
           <t>C | 531呎 (3房)
 $1267万
 $23,856/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -16631,7 +16631,7 @@
           <t>D | 406呎 (2房)
 $910万
 $22,422/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -16639,7 +16639,7 @@
           <t>E | 408呎 (2房)
 $955万
 $23,398/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -16647,7 +16647,7 @@
           <t>F | 266呎 (1房)
 $611万
 $22,984/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -16655,7 +16655,7 @@
           <t>G | 274呎 (1房)
 $682万
 $24,885/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -16663,7 +16663,7 @@
           <t>H | 265呎 (1房)
 $557万
 $21,009/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -16671,7 +16671,7 @@
           <t>J | 347呎 (2房)
 $731万
 $21,063/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -16679,7 +16679,7 @@
           <t>K | 348呎 (2房)
 $779万
 $22,389/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -16687,7 +16687,7 @@
           <t>L | 356呎 (2房)
 $742万
 $20,849/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,152/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -16718,7 +16718,7 @@
           <t>C | 531呎 (3房)
 $1254万
 $23,610/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -16726,7 +16726,7 @@
           <t>D | 406呎 (2房)
 $901万
 $22,192/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -16734,7 +16734,7 @@
           <t>E | 408呎 (2房)
 $945万
 $23,157/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -16742,7 +16742,7 @@
           <t>F | 266呎 (1房)
 $605万
 $22,747/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -16750,7 +16750,7 @@
           <t>G | 274呎 (1房)
 $635万
 $23,193/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -16758,7 +16758,7 @@
           <t>H | 265呎 (1房)
 $554万
 $20,887/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -16766,7 +16766,7 @@
           <t>J | 347呎 (2房)
 $727万
 $20,939/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -16774,7 +16774,7 @@
           <t>K | 348呎 (2房)
 $721万
 $20,728/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -16782,7 +16782,7 @@
           <t>L | 356呎 (2房)
 $738万
 $20,725/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
           <t>A | 600呎 (4+房)
 $1585万
 $26,417/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -16805,7 +16805,7 @@
           <t>B | 534呎 (3房)
 $1229万
 $23,017/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -16813,7 +16813,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-03月-27日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -16821,7 +16821,7 @@
           <t>D | 406呎 (2房)
 $896万
 $22,061/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -16829,7 +16829,7 @@
           <t>E | 408呎 (2房)
 $939万
 $23,021/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -16837,7 +16837,7 @@
           <t>F | 266呎 (1房)
 $602万
 $22,632/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -16845,7 +16845,7 @@
           <t>G | 274呎 (1房)
 $671万
 $24,474/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -16853,7 +16853,7 @@
           <t>H | 265呎 (1房)
 $550万
 $20,768/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -16861,7 +16861,7 @@
           <t>J | 347呎 (2房)
 $722万
 $20,812/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -16869,7 +16869,7 @@
           <t>K | 348呎 (2房)
 $729万
 $20,948/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -16877,7 +16877,7 @@
           <t>L | 356呎 (2房)
 $733万
 $20,601/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
           <t>A | 600呎 (4+房)
 $1555万
 $25,912/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -16900,7 +16900,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,137/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -16908,7 +16908,7 @@
           <t>C | 531呎 (3房)
 $1192万
 $22,446/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -16916,7 +16916,7 @@
           <t>D | 406呎 (2房)
 $890万
 $21,933/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -16924,7 +16924,7 @@
           <t>E | 408呎 (2房)
 $934万
 $22,884/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -16932,7 +16932,7 @@
           <t>F | 266呎 (1房)
 $600万
 $22,544/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -16940,7 +16940,7 @@
           <t>G | 274呎 (1房)
 $678万
 $24,731/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -16948,7 +16948,7 @@
           <t>H | 265呎 (1房)
 $549万
 $20,710/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -16956,7 +16956,7 @@
           <t>J | 347呎 (2房)
 $694万
 $20,005/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -16964,7 +16964,7 @@
           <t>K | 348呎 (2房)
 $715万
 $20,542/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -16972,7 +16972,7 @@
           <t>L | 356呎 (2房)
 $731万
 $20,538/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
           <t>B | 534呎 (3房)
 $1257万
 $23,547/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -17003,7 +17003,7 @@
           <t>C | 531呎 (3房)
 $1172万
 $22,078/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -17011,7 +17011,7 @@
           <t>D | 406呎 (2房)
 $938万
 $23,096/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -17019,7 +17019,7 @@
           <t>E | 408呎 (2房)
 $934万
 $22,884/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -17027,7 +17027,7 @@
           <t>F | 266呎 (1房)
 $600万
 $22,544/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -17035,7 +17035,7 @@
           <t>G | 274呎 (1房)
 $667万
 $24,326/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -17043,7 +17043,7 @@
           <t>H | 265呎 (1房)
 $589万
 $22,211/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -17051,7 +17051,7 @@
           <t>J | 347呎 (2房)
 $694万
 $20,005/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -17059,7 +17059,7 @@
           <t>K | 348呎 (2房)
 $715万
 $20,542/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -17067,7 +17067,7 @@
           <t>L | 356呎 (2房)
 $731万
 $20,538/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
           <t>A | 600呎 (4+房)
 $1551万
 $25,848/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -17090,7 +17090,7 @@
           <t>B | 534呎 (3房)
 $1147万
 $21,472/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -17098,7 +17098,7 @@
           <t>C | 531呎 (3房)
 $1158万
 $21,814/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -17106,7 +17106,7 @@
           <t>D | 406呎 (2房)
 $880万
 $21,671/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -17114,7 +17114,7 @@
           <t>E | 408呎 (2房)
 $908万
 $22,264/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -17122,7 +17122,7 @@
           <t>F | 266呎 (1房)
 $613万
 $23,035/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -17130,7 +17130,7 @@
           <t>G | 274呎 (1房)
 $658万
 $24,031/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -17138,7 +17138,7 @@
           <t>H | 265呎 (1房)
 $552万
 $20,832/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -17146,7 +17146,7 @@
           <t>J | 347呎 (2房)
 $686万
 $19,766/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -17154,7 +17154,7 @@
           <t>K | 348呎 (2房)
 $688万
 $19,761/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -17162,7 +17162,7 @@
           <t>L | 356呎 (2房)
 $722万
 $20,290/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -17185,7 +17185,7 @@
           <t>B | 534呎 (3房)
 $1143万
 $21,408/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -17193,7 +17193,7 @@
           <t>C | 531呎 (3房)
 $1155万
 $21,747/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -17201,7 +17201,7 @@
           <t>D | 406呎 (2房)
 $875万
 $21,540/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -17209,7 +17209,7 @@
           <t>E | 408呎 (2房)
 $893万
 $21,887/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -17217,7 +17217,7 @@
           <t>F | 266呎 (1房)
 $609万
 $22,892/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -17225,7 +17225,7 @@
           <t>G | 274呎 (1房)
 $616万
 $22,497/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -17233,7 +17233,7 @@
           <t>H | 265呎 (1房)
 $550万
 $20,769/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -17241,7 +17241,7 @@
           <t>J | 347呎 (2房)
 $684万
 $19,704/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -17249,7 +17249,7 @@
           <t>K | 348呎 (2房)
 $708万
 $20,358/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -17257,7 +17257,7 @@
           <t>L | 356呎 (2房)
 $725万
 $20,355/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
           <t>A | 600呎 (4+房)
 $1515万
 $25,250/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -17280,7 +17280,7 @@
           <t>B | 534呎 (3房)
 $1136万
 $21,280/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -17288,7 +17288,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,195/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -17296,7 +17296,7 @@
           <t>D | 406呎 (2房)
 $867万
 $21,345/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -17304,7 +17304,7 @@
           <t>E | 408呎 (2房)
 $885万
 $21,686/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -17312,7 +17312,7 @@
           <t>F | 266呎 (1房)
 $624万
 $23,442/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -17320,7 +17320,7 @@
           <t>G | 274呎 (1房)
 $617万
 $22,534/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -17328,7 +17328,7 @@
           <t>H | 265呎 (1房)
 $531万
 $20,041/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -17336,7 +17336,7 @@
           <t>J | 347呎 (2房)
 $682万
 $19,644/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -17344,7 +17344,7 @@
           <t>K | 348呎 (2房)
 $706万
 $20,294/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -17352,7 +17352,7 @@
           <t>L | 356呎 (2房)
 $718万
 $20,179/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17375,7 @@
           <t>B | 534呎 (3房)
 $1176万
 $22,023/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -17383,7 +17383,7 @@
           <t>C | 531呎 (3房)
 $1168万
 $21,992/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -17391,7 +17391,7 @@
           <t>D | 406呎 (2房)
 $851万
 $20,955/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -17399,7 +17399,7 @@
           <t>E | 408呎 (2房)
 $868万
 $21,287/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -17407,7 +17407,7 @@
           <t>F | 266呎 (1房)
 $592万
 $22,267/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -17415,7 +17415,7 @@
           <t>G | 274呎 (1房)
 $599万
 $21,869/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -17423,7 +17423,7 @@
           <t>H | 265呎 (1房)
 $529万
 $19,980/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -17431,7 +17431,7 @@
           <t>J | 347呎 (2房)
 $680万
 $19,608/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -17439,7 +17439,7 @@
           <t>K | 348呎 (2房)
 $681万
 $19,580/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -17447,7 +17447,7 @@
           <t>L | 356呎 (2房)
 $716万
 $20,119/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17470,7 @@
           <t>B | 534呎 (3房)
 $1123万
 $21,022/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -17478,7 +17478,7 @@
           <t>C | 531呎 (3房)
 $1164万
 $21,922/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -17486,7 +17486,7 @@
           <t>D | 406呎 (2房)
 $845万
 $20,824/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -17494,7 +17494,7 @@
           <t>E | 408呎 (2房)
 $863万
 $21,154/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -17502,7 +17502,7 @@
           <t>F | 266呎 (1房)
 $589万
 $22,124/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -17510,7 +17510,7 @@
           <t>G | 274呎 (1房)
 $595万
 $21,728/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -17518,7 +17518,7 @@
           <t>H | 265呎 (1房)
 $528万
 $19,922/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -17526,7 +17526,7 @@
           <t>J | 347呎 (2房)
 $703万
 $20,246/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -17534,7 +17534,7 @@
           <t>K | 348呎 (2房)
 $679万
 $19,521/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -17542,7 +17542,7 @@
           <t>L | 356呎 (2房)
 $714万
 $20,055/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17565,7 +17565,7 @@
           <t>B | 534呎 (3房)
 $1119万
 $20,958/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -17573,7 +17573,7 @@
           <t>C | 531呎 (3房)
 $1160万
 $21,854/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -17581,7 +17581,7 @@
           <t>D | 406呎 (2房)
 $840万
 $20,693/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -17589,7 +17589,7 @@
           <t>E | 408呎 (2房)
 $872万
 $21,372/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -17597,7 +17597,7 @@
           <t>F | 266呎 (1房)
 $604万
 $22,718/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -17605,7 +17605,7 @@
           <t>G | 274呎 (1房)
 $592万
 $21,590/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -17613,7 +17613,7 @@
           <t>H | 265呎 (1房)
 $532万
 $20,082/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -17621,7 +17621,7 @@
           <t>J | 347呎 (2房)
 $665万
 $19,170/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -17629,7 +17629,7 @@
           <t>K | 348呎 (2房)
 $677万
 $19,459/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -17637,7 +17637,7 @@
           <t>L | 356呎 (2房)
 $712万
 $19,995/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
           <t>A | 600呎 (4+房)
 $1488万
 $24,800/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -17660,7 +17660,7 @@
           <t>B | 534呎 (3房)
 $1116万
 $20,894/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -17668,7 +17668,7 @@
           <t>C | 531呎 (3房)
 $1163万
 $21,907/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -17676,7 +17676,7 @@
           <t>D | 406呎 (2房)
 $835万
 $20,563/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -17684,7 +17684,7 @@
           <t>E | 408呎 (2房)
 $852万
 $20,888/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -17692,7 +17692,7 @@
           <t>F | 266呎 (1房)
 $581万
 $21,847/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -17700,7 +17700,7 @@
           <t>G | 274呎 (1房)
 $591万
 $21,568/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -17708,7 +17708,7 @@
           <t>H | 265呎 (1房)
 $548万
 $20,683/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -17716,7 +17716,7 @@
           <t>J | 347呎 (2房)
 $663万
 $19,113/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -17724,7 +17724,7 @@
           <t>K | 348呎 (2房)
 $675万
 $19,399/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -17732,7 +17732,7 @@
           <t>L | 356呎 (2房)
 $717万
 $20,153/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
           <t>B | 534呎 (3房)
 $1153万
 $21,590/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -17763,7 +17763,7 @@
           <t>C | 531呎 (3房)
 $1157万
 $21,786/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -17771,7 +17771,7 @@
           <t>D | 406呎 (2房)
 $835万
 $20,563/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -17779,7 +17779,7 @@
           <t>E | 408呎 (2房)
 $852万
 $20,888/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -17787,7 +17787,7 @@
           <t>F | 266呎 (1房)
 $581万
 $21,847/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -17795,7 +17795,7 @@
           <t>G | 274呎 (1房)
 $597万
 $21,806/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -17803,7 +17803,7 @@
           <t>H | 265呎 (1房)
 $525万
 $19,803/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -17811,7 +17811,7 @@
           <t>J | 347呎 (2房)
 $663万
 $19,113/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -17819,7 +17819,7 @@
           <t>K | 348呎 (2房)
 $675万
 $19,399/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -17827,7 +17827,7 @@
           <t>L | 356呎 (2房)
 $710万
 $19,931/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
           <t>A | 600呎 (4+房)
 $1478万
 $24,633/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -17850,7 +17850,7 @@
           <t>B | 534呎 (3房)
 $1109万
 $20,766/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -17858,7 +17858,7 @@
           <t>C | 531呎 (3房)
 $1183万
 $22,280/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -17866,7 +17866,7 @@
           <t>D | 406呎 (2房)
 $824万
 $20,303/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -17874,7 +17874,7 @@
           <t>E | 408呎 (2房)
 $869万
 $21,310/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -17882,7 +17882,7 @@
           <t>F | 266呎 (1房)
 $574万
 $21,566/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -17890,7 +17890,7 @@
           <t>G | 274呎 (1房)
 $580万
 $21,170/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -17898,7 +17898,7 @@
           <t>H | 265呎 (1房)
 $523万
 $19,746/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -17906,7 +17906,7 @@
           <t>J | 347呎 (2房)
 $659万
 $18,993/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -17914,7 +17914,7 @@
           <t>K | 348呎 (2房)
 $671万
 $19,278/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -17922,7 +17922,7 @@
           <t>L | 356呎 (2房)
 $705万
 $19,808/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
           <t>B | 534呎 (3房)
 $1105万
 $20,702/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -17953,7 +17953,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -17961,7 +17961,7 @@
           <t>D | 406呎 (2房)
 $819万
 $20,172/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -17969,7 +17969,7 @@
           <t>E | 408呎 (2房)
 $836万
 $20,488/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -17977,7 +17977,7 @@
           <t>F | 266呎 (1房)
 $570万
 $21,424/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -17985,7 +17985,7 @@
           <t>G | 274呎 (1房)
 $576万
 $21,028/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -17993,7 +17993,7 @@
           <t>H | 265呎 (1房)
 $523万
 $19,729/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -18001,7 +18001,7 @@
           <t>J | 347呎 (2房)
 $655万
 $18,882/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -18009,7 +18009,7 @@
           <t>K | 348呎 (2房)
 $666万
 $19,148/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -18017,7 +18017,7 @@
           <t>L | 356呎 (2房)
 $701万
 $19,681/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
           <t>A | 560呎 (4+房)
 $1608万
 $28,714/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -18040,7 +18040,7 @@
           <t>B | 498呎 (3房)
 $1285万
 $25,800/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -18048,7 +18048,7 @@
           <t>C | 493呎 (3房)
 $1267万
 $25,700/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -18056,7 +18056,7 @@
           <t>D | 369呎 (2房)
 $948万
 $25,700/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>E | 370呎 (2房)
 $940万
 $25,400/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>G | 236呎 (1房)
 $642万
 $27,200/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -18096,7 +18096,7 @@
           <t>J | 309呎 (2房)
 $791万
 $25,600/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -18104,7 +18104,7 @@
           <t>K | 310呎 (2房)
 $784万
 $25,300/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -18112,7 +18112,7 @@
           <t>L | 319呎 (2房)
 $740万
 $23,200/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首汇.xlsx
+++ b/files/九龙-红磡-首汇.xlsx
@@ -673,7 +673,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -800,14 +800,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>7106940</v>
+        <v>7896600</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>19963</v>
+        <v>22181</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -862,14 +862,14 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>7460100</v>
+        <v>8289000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>21437</v>
+        <v>23819</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1414,14 +1414,14 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>26838000</v>
+        <v>29820000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>31574</v>
+        <v>35082</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1476,14 +1476,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>6976170</v>
+        <v>7751300</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>19596</v>
+        <v>21773</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6569100</v>
+        <v>7299000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>18877</v>
+        <v>20974</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6450030</v>
+        <v>7166700</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>18588</v>
+        <v>20653</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5167800</v>
+        <v>5742000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>19501</v>
+        <v>21668</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1724,14 +1724,14 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>6046650</v>
+        <v>6718500</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>22068</v>
+        <v>24520</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1786,14 +1786,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5751810</v>
+        <v>6390900</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>21623</v>
+        <v>24026</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1848,14 +1848,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>8745570</v>
+        <v>9717300</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>21435</v>
+        <v>23817</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1910,14 +1910,14 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>9016920</v>
+        <v>10018800</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>22209</v>
+        <v>24677</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>12317220</v>
+        <v>13685800</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>23196</v>
+        <v>25774</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>6953580</v>
+        <v>7726200</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>19533</v>
+        <v>21703</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>6512400</v>
+        <v>7236000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>18714</v>
+        <v>20793</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2290,14 +2290,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>6394140</v>
+        <v>7104600</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>18427</v>
+        <v>20474</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2352,14 +2352,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>5295690</v>
+        <v>5884100</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>19984</v>
+        <v>22204</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2414,14 +2414,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5977800</v>
+        <v>6642000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>21817</v>
+        <v>24241</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2476,14 +2476,14 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5687010</v>
+        <v>6318900</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>21380</v>
+        <v>23755</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>8647560</v>
+        <v>9608400</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>21195</v>
+        <v>23550</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2600,14 +2600,14 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>9213660</v>
+        <v>10237400</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>22694</v>
+        <v>25215</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>11786310</v>
+        <v>13095900</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>22196</v>
+        <v>24663</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2724,14 +2724,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11030580</v>
+        <v>12256200</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>20657</v>
+        <v>22952</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2786,14 +2786,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>14670000</v>
+        <v>16300000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>24450</v>
+        <v>27167</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>7047540</v>
+        <v>7830600</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>19796</v>
+        <v>21996</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>6493770</v>
+        <v>7215300</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>18660</v>
+        <v>20734</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2972,14 +2972,14 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>6376320</v>
+        <v>7084800</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>18376</v>
+        <v>20417</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3034,14 +3034,14 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5110290</v>
+        <v>5678100</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>19284</v>
+        <v>21427</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3096,14 +3096,14 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>5943780</v>
+        <v>6604200</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>21693</v>
+        <v>24103</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3158,14 +3158,14 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>5655420</v>
+        <v>6283800</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>21261</v>
+        <v>23623</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>9161730</v>
+        <v>10179700</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>22566</v>
+        <v>25073</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3344,14 +3344,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11719080</v>
+        <v>13021200</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>22070</v>
+        <v>24522</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3406,14 +3406,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>10968210</v>
+        <v>12186900</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>20540</v>
+        <v>22822</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3468,14 +3468,14 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>14652000</v>
+        <v>16280000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>24420</v>
+        <v>27133</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3530,14 +3530,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6760260</v>
+        <v>7511400</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>18989</v>
+        <v>21099</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3592,14 +3592,14 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>6650730</v>
+        <v>7389700</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>19111</v>
+        <v>21235</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>6320430</v>
+        <v>7022700</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>18214</v>
+        <v>20238</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>5067360</v>
+        <v>5630400</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>19122</v>
+        <v>21247</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>5883030</v>
+        <v>6536700</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>21471</v>
+        <v>23857</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3840,14 +3840,14 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>5598720</v>
+        <v>6220800</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>21048</v>
+        <v>23386</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3902,14 +3902,14 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>8513100</v>
+        <v>9459000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>20865</v>
+        <v>23184</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>8777970</v>
+        <v>9753300</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>21621</v>
+        <v>24023</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>11601630</v>
+        <v>12890700</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>21849</v>
+        <v>24276</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4088,14 +4088,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>10859670</v>
+        <v>12066300</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>20336</v>
+        <v>22596</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4220,14 +4220,14 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>6794370</v>
+        <v>7549300</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>19085</v>
+        <v>21206</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -4344,14 +4344,14 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>6283170</v>
+        <v>6981300</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>18107</v>
+        <v>20119</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4406,14 +4406,14 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>5039010</v>
+        <v>5598900</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>19015</v>
+        <v>21128</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4468,14 +4468,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>5848200</v>
+        <v>6498000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>21344</v>
+        <v>23715</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>5751810</v>
+        <v>6390900</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>21623</v>
+        <v>24026</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>8464500</v>
+        <v>9405000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>20746</v>
+        <v>23051</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4654,14 +4654,14 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>8287920</v>
+        <v>9208800</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>20414</v>
+        <v>22682</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="5" t="n">
-        <v>11534400</v>
+        <v>12816000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>21722</v>
+        <v>24136</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
-        <v>10798110</v>
+        <v>11997900</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>20221</v>
+        <v>22468</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>6680070</v>
+        <v>7422300</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>18764</v>
+        <v>20849</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4972,14 +4972,14 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>7012170</v>
+        <v>7791300</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>20150</v>
+        <v>22389</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -5034,14 +5034,14 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>6578010</v>
+        <v>7308900</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>18957</v>
+        <v>21063</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5096,14 +5096,14 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5010660</v>
+        <v>5567400</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>18908</v>
+        <v>21009</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5158,14 +5158,14 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>6136560</v>
+        <v>6818400</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>22396</v>
+        <v>24885</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5220,14 +5220,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>5502330</v>
+        <v>6113700</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>20685</v>
+        <v>22984</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>8591670</v>
+        <v>9546300</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>21058</v>
+        <v>23398</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>8193150</v>
+        <v>9103500</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>20180</v>
+        <v>22422</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="5" t="n">
-        <v>11400750</v>
+        <v>12667500</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>21470</v>
+        <v>23856</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5468,14 +5468,14 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>11241180</v>
+        <v>12490200</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>21051</v>
+        <v>23390</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>6640380</v>
+        <v>7378200</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>18653</v>
+        <v>20725</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5662,14 +5662,14 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>6492150</v>
+        <v>7213500</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>18656</v>
+        <v>20728</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5724,14 +5724,14 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>6539130</v>
+        <v>7265700</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>18845</v>
+        <v>20939</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5786,14 +5786,14 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>4981500</v>
+        <v>5535000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>18798</v>
+        <v>20887</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5848,14 +5848,14 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>5719410</v>
+        <v>6354900</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>20874</v>
+        <v>23193</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>5445630</v>
+        <v>6050700</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>20472</v>
+        <v>22747</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5972,14 +5972,14 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>8503380</v>
+        <v>9448200</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>20842</v>
+        <v>23157</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6034,14 +6034,14 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>8108910</v>
+        <v>9009900</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>19973</v>
+        <v>22192</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>11283300</v>
+        <v>12537000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>21249</v>
+        <v>23610</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>11126970</v>
+        <v>12363300</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>20837</v>
+        <v>23152</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6290,14 +6290,14 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>6600690</v>
+        <v>7334100</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>18541</v>
+        <v>20601</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>6560820</v>
+        <v>7289800</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>18853</v>
+        <v>20948</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>6499440</v>
+        <v>7221600</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>18730</v>
+        <v>20812</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6476,14 +6476,14 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>4953150</v>
+        <v>5503500</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>18691</v>
+        <v>20768</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6538,14 +6538,14 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>6035310</v>
+        <v>6705900</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>22027</v>
+        <v>24474</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>5418090</v>
+        <v>6020100</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>20369</v>
+        <v>22632</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6662,14 +6662,14 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>8453160</v>
+        <v>9392400</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>20719</v>
+        <v>23021</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6724,14 +6724,14 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>8061120</v>
+        <v>8956800</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>19855</v>
+        <v>22061</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6786,14 +6786,14 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="5" t="n">
-        <v>10614240</v>
+        <v>11793600</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>19989</v>
+        <v>22210</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>11062170</v>
+        <v>12291300</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>20716</v>
+        <v>23017</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6910,14 +6910,14 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="5" t="n">
-        <v>14265000</v>
+        <v>15850000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>23775</v>
+        <v>26417</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -6972,14 +6972,14 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>6580440</v>
+        <v>7311600</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>18484</v>
+        <v>20538</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -7034,14 +7034,14 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>6433830</v>
+        <v>7148700</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>18488</v>
+        <v>20542</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7096,14 +7096,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>6247530</v>
+        <v>6941700</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>18004</v>
+        <v>20005</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>4939380</v>
+        <v>5488200</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>18639</v>
+        <v>20710</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7220,14 +7220,14 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>6098760</v>
+        <v>6776400</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>22258</v>
+        <v>24731</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7282,14 +7282,14 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>5397030</v>
+        <v>5996700</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>20290</v>
+        <v>22544</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7344,14 +7344,14 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>8402940</v>
+        <v>9336600</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>20595</v>
+        <v>22884</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7406,14 +7406,14 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="5" t="n">
-        <v>8014140</v>
+        <v>8904600</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>19739</v>
+        <v>21933</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -7468,14 +7468,14 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="5" t="n">
-        <v>10726830</v>
+        <v>11918700</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>20201</v>
+        <v>22446</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -7530,14 +7530,14 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="5" t="n">
-        <v>11119500</v>
+        <v>12355000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>20823</v>
+        <v>23137</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7592,14 +7592,14 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>13992570</v>
+        <v>15547300</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>23321</v>
+        <v>25912</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -7654,14 +7654,14 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>6580440</v>
+        <v>7311600</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>18484</v>
+        <v>20538</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -7716,14 +7716,14 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="5" t="n">
-        <v>6433830</v>
+        <v>7148700</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>18488</v>
+        <v>20542</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -7778,14 +7778,14 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>6247530</v>
+        <v>6941700</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>18004</v>
+        <v>20005</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7840,14 +7840,14 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="5" t="n">
-        <v>5297400</v>
+        <v>5886000</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>19990</v>
+        <v>22211</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -7902,14 +7902,14 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>5998860</v>
+        <v>6665400</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>21894</v>
+        <v>24326</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -7964,14 +7964,14 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>5397030</v>
+        <v>5996700</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>20290</v>
+        <v>22544</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8026,14 +8026,14 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="5" t="n">
-        <v>8402940</v>
+        <v>9336600</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>20595</v>
+        <v>22884</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
@@ -8088,14 +8088,14 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="5" t="n">
-        <v>8439390</v>
+        <v>9377100</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>20787</v>
+        <v>23096</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -8150,14 +8150,14 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="5" t="n">
-        <v>10551060</v>
+        <v>11723400</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>19870</v>
+        <v>22078</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8212,14 +8212,14 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="5" t="n">
-        <v>11316510</v>
+        <v>12573900</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>21192</v>
+        <v>23547</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8344,14 +8344,14 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="5" t="n">
-        <v>6501060</v>
+        <v>7223400</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>18261</v>
+        <v>20290</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8406,14 +8406,14 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>6189210</v>
+        <v>6876900</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>17785</v>
+        <v>19761</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>6173010</v>
+        <v>6858900</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>17790</v>
+        <v>19766</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
@@ -8530,14 +8530,14 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="5" t="n">
-        <v>4968360</v>
+        <v>5520400</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>18749</v>
+        <v>20832</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -8592,14 +8592,14 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>5925960</v>
+        <v>6584400</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>21628</v>
+        <v>24031</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -8654,14 +8654,14 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="5" t="n">
-        <v>5514480</v>
+        <v>6127200</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>20731</v>
+        <v>23035</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
@@ -8716,14 +8716,14 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>8175240</v>
+        <v>9083600</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>20037</v>
+        <v>22264</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -8778,14 +8778,14 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="5" t="n">
-        <v>7918560</v>
+        <v>8798400</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>19504</v>
+        <v>21671</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
@@ -8840,14 +8840,14 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="5" t="n">
-        <v>10424700</v>
+        <v>11583000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>19632</v>
+        <v>21814</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -8902,14 +8902,14 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>10319400</v>
+        <v>11466000</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>19325</v>
+        <v>21472</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>13958100</v>
+        <v>15509000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>23264</v>
+        <v>25848</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9026,14 +9026,14 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>6521670</v>
+        <v>7246300</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>18319</v>
+        <v>20355</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>6376230</v>
+        <v>7084700</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>18322</v>
+        <v>20358</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9150,14 +9150,14 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>6153570</v>
+        <v>6837300</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>17734</v>
+        <v>19704</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9212,14 +9212,14 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>4953330</v>
+        <v>5503700</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>18692</v>
+        <v>20769</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="5" t="n">
-        <v>5547690</v>
+        <v>6164100</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>20247</v>
+        <v>22497</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9336,14 +9336,14 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="5" t="n">
-        <v>5480460</v>
+        <v>6089400</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>20603</v>
+        <v>22892</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9398,14 +9398,14 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="5" t="n">
-        <v>8036820</v>
+        <v>8929800</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>19698</v>
+        <v>21887</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9460,14 +9460,14 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>7870770</v>
+        <v>8745300</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>19386</v>
+        <v>21540</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9522,14 +9522,14 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>10393110</v>
+        <v>11547900</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>19573</v>
+        <v>21747</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9584,14 +9584,14 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>10288620</v>
+        <v>11431800</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>19267</v>
+        <v>21408</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>6465420</v>
+        <v>7183800</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>18161</v>
+        <v>20179</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9778,14 +9778,14 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>6356160</v>
+        <v>7062400</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>18265</v>
+        <v>20294</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9840,14 +9840,14 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="5" t="n">
-        <v>6134940</v>
+        <v>6816600</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>17680</v>
+        <v>19644</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -9902,14 +9902,14 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>4779810</v>
+        <v>5310900</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>18037</v>
+        <v>20041</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -9964,14 +9964,14 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="5" t="n">
-        <v>5556870</v>
+        <v>6174300</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>20281</v>
+        <v>22534</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -10026,14 +10026,14 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>5612040</v>
+        <v>6235600</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>21098</v>
+        <v>23442</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -10088,14 +10088,14 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>7963110</v>
+        <v>8847900</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>19517</v>
+        <v>21686</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10150,14 +10150,14 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>7799490</v>
+        <v>8666100</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>19211</v>
+        <v>21345</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10212,14 +10212,14 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>10606950</v>
+        <v>11785500</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>19975</v>
+        <v>22195</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10274,14 +10274,14 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="5" t="n">
-        <v>10227060</v>
+        <v>11363400</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>19152</v>
+        <v>21280</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
@@ -10336,14 +10336,14 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>13635000</v>
+        <v>15150000</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>22725</v>
+        <v>25250</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10398,14 +10398,14 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>6445980</v>
+        <v>7162200</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>18107</v>
+        <v>20119</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -10460,14 +10460,14 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>6132510</v>
+        <v>6813900</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>17622</v>
+        <v>19580</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10522,14 +10522,14 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>6123600</v>
+        <v>6804000</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>17647</v>
+        <v>19608</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -10584,14 +10584,14 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>4765230</v>
+        <v>5294700</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>17982</v>
+        <v>19980</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10646,14 +10646,14 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>5392980</v>
+        <v>5992200</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>19682</v>
+        <v>21869</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -10708,14 +10708,14 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>5330610</v>
+        <v>5922900</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>20040</v>
+        <v>22267</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -10770,14 +10770,14 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>7816500</v>
+        <v>8685000</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>19158</v>
+        <v>21287</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -10832,14 +10832,14 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="5" t="n">
-        <v>7656930</v>
+        <v>8507700</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>18859</v>
+        <v>20955</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -10894,14 +10894,14 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="5" t="n">
-        <v>10509750</v>
+        <v>11677500</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>19792</v>
+        <v>21992</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -10956,14 +10956,14 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="5" t="n">
-        <v>10584270</v>
+        <v>11760300</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>19821</v>
+        <v>22023</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
@@ -11088,14 +11088,14 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="5" t="n">
-        <v>6425730</v>
+        <v>7139700</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>18050</v>
+        <v>20055</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -11150,14 +11150,14 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>6113880</v>
+        <v>6793200</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>17569</v>
+        <v>19521</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11212,14 +11212,14 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>6322860</v>
+        <v>7025400</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>18221</v>
+        <v>20246</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11274,14 +11274,14 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>4751460</v>
+        <v>5279400</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>17930</v>
+        <v>19922</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -11336,14 +11336,14 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>5358150</v>
+        <v>5953500</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>19555</v>
+        <v>21728</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
@@ -11398,14 +11398,14 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="5" t="n">
-        <v>5296590</v>
+        <v>5885100</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>19912</v>
+        <v>22124</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11460,14 +11460,14 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>7767900</v>
+        <v>8631000</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>19039</v>
+        <v>21154</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -11522,14 +11522,14 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>7609140</v>
+        <v>8454600</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>18742</v>
+        <v>20824</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -11584,14 +11584,14 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>10476540</v>
+        <v>11640600</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>19730</v>
+        <v>21922</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -11646,14 +11646,14 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>10103130</v>
+        <v>11225700</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>18920</v>
+        <v>21022</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11778,14 +11778,14 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>6406290</v>
+        <v>7118100</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>17995</v>
+        <v>19995</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -11840,14 +11840,14 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>6094440</v>
+        <v>6771600</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>17513</v>
+        <v>19459</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11902,14 +11902,14 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>5986710</v>
+        <v>6651900</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>17253</v>
+        <v>19170</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -11964,14 +11964,14 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>4789440</v>
+        <v>5321600</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>18073</v>
+        <v>20082</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12026,14 +12026,14 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K182" s="5" t="n">
-        <v>5324130</v>
+        <v>5915700</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>19431</v>
+        <v>21590</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -12088,14 +12088,14 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K183" s="5" t="n">
-        <v>5438790</v>
+        <v>6043100</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>20447</v>
+        <v>22718</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -12150,14 +12150,14 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K184" s="5" t="n">
-        <v>7847910</v>
+        <v>8719900</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>19235</v>
+        <v>21372</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12212,14 +12212,14 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>7561350</v>
+        <v>8401500</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>18624</v>
+        <v>20693</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12274,14 +12274,14 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>10444140</v>
+        <v>11604600</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>19669</v>
+        <v>21854</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12336,14 +12336,14 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>10072350</v>
+        <v>11191500</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>18862</v>
+        <v>20958</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12468,14 +12468,14 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>6456960</v>
+        <v>7174400</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>18138</v>
+        <v>20153</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
@@ -12530,14 +12530,14 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>6075810</v>
+        <v>6750900</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>17459</v>
+        <v>19399</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12592,14 +12592,14 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K191" s="5" t="n">
-        <v>5968890</v>
+        <v>6632100</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>17201</v>
+        <v>19113</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12654,14 +12654,14 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>4932990</v>
+        <v>5481100</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>18615</v>
+        <v>20683</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -12716,14 +12716,14 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K193" s="5" t="n">
-        <v>5318640</v>
+        <v>5909600</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>19411</v>
+        <v>21568</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -12778,14 +12778,14 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>5230170</v>
+        <v>5811300</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>19662</v>
+        <v>21847</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -12840,14 +12840,14 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>7669890</v>
+        <v>8522100</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>18799</v>
+        <v>20888</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -12902,14 +12902,14 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>7513560</v>
+        <v>8348400</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>18506</v>
+        <v>20563</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -12964,14 +12964,14 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K197" s="5" t="n">
-        <v>10469520</v>
+        <v>11632800</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>19717</v>
+        <v>21907</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -13026,14 +13026,14 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>10041570</v>
+        <v>11157300</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>18804</v>
+        <v>20894</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -13088,14 +13088,14 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K199" s="5" t="n">
-        <v>13392000</v>
+        <v>14880000</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>22320</v>
+        <v>24800</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13150,14 +13150,14 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>6386040</v>
+        <v>7095600</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>17938</v>
+        <v>19931</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13212,14 +13212,14 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>6075810</v>
+        <v>6750900</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>17459</v>
+        <v>19399</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -13274,14 +13274,14 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K202" s="5" t="n">
-        <v>5968890</v>
+        <v>6632100</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>17201</v>
+        <v>19113</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13336,14 +13336,14 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K203" s="5" t="n">
-        <v>4723110</v>
+        <v>5247900</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>17823</v>
+        <v>19803</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13398,14 +13398,14 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>5377410</v>
+        <v>5974900</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>19626</v>
+        <v>21806</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13460,14 +13460,14 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>5230170</v>
+        <v>5811300</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>19662</v>
+        <v>21847</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13522,14 +13522,14 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
-        <v>7669890</v>
+        <v>8522100</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>18799</v>
+        <v>20888</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -13584,14 +13584,14 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>7513560</v>
+        <v>8348400</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>18506</v>
+        <v>20563</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -13646,14 +13646,14 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>10411740</v>
+        <v>11568600</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>19608</v>
+        <v>21786</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
@@ -13708,14 +13708,14 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K209" s="5" t="n">
-        <v>10376280</v>
+        <v>11529200</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>19431</v>
+        <v>21590</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -13840,14 +13840,14 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K211" s="5" t="n">
-        <v>6346350</v>
+        <v>7051500</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>17827</v>
+        <v>19808</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
@@ -13902,14 +13902,14 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K212" s="5" t="n">
-        <v>6037740</v>
+        <v>6708600</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>17350</v>
+        <v>19278</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -13964,14 +13964,14 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>5931630</v>
+        <v>6590700</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>17094</v>
+        <v>18993</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -14026,14 +14026,14 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>4709340</v>
+        <v>5232600</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>17771</v>
+        <v>19746</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14088,14 +14088,14 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>5220450</v>
+        <v>5800500</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>19053</v>
+        <v>21170</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -14150,14 +14150,14 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K216" s="5" t="n">
-        <v>5162940</v>
+        <v>5736600</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>19410</v>
+        <v>21566</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -14212,14 +14212,14 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K217" s="5" t="n">
-        <v>7825050</v>
+        <v>8694500</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>19179</v>
+        <v>21310</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -14274,14 +14274,14 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
-        <v>7418790</v>
+        <v>8243100</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>18273</v>
+        <v>20303</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -14336,14 +14336,14 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K219" s="5" t="n">
-        <v>10647450</v>
+        <v>11830500</v>
       </c>
       <c r="L219" s="5" t="n">
-        <v>20052</v>
+        <v>22280</v>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
@@ -14398,14 +14398,14 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K220" s="5" t="n">
-        <v>9980010</v>
+        <v>11088900</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>18689</v>
+        <v>20766</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14460,14 +14460,14 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>13302000</v>
+        <v>14780000</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>22170</v>
+        <v>24633</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -14522,14 +14522,14 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
-        <v>6305850</v>
+        <v>7006500</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>17713</v>
+        <v>19681</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
@@ -14584,14 +14584,14 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>5997240</v>
+        <v>6663600</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>17233</v>
+        <v>19148</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
@@ -14646,14 +14646,14 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K224" s="5" t="n">
-        <v>5896800</v>
+        <v>6552000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>16994</v>
+        <v>18882</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -14708,14 +14708,14 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>4705290</v>
+        <v>5228100</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>17756</v>
+        <v>19729</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -14770,14 +14770,14 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K226" s="5" t="n">
-        <v>5185620</v>
+        <v>5761800</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>18926</v>
+        <v>21028</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
@@ -14832,14 +14832,14 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>5128920</v>
+        <v>5698800</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>19282</v>
+        <v>21424</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -14894,14 +14894,14 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K228" s="5" t="n">
-        <v>7523280</v>
+        <v>8359200</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>18439</v>
+        <v>20488</v>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
@@ -14956,14 +14956,14 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K229" s="5" t="n">
-        <v>7371000</v>
+        <v>8190000</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>18155</v>
+        <v>20172</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -15018,14 +15018,14 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K230" s="5" t="n">
-        <v>10614240</v>
+        <v>11793600</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>19989</v>
+        <v>22210</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15080,14 +15080,14 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>9949230</v>
+        <v>11054700</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>18632</v>
+        <v>20702</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15212,14 +15212,14 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>6660720</v>
+        <v>7400800</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>20880</v>
+        <v>23200</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -15274,14 +15274,14 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
-        <v>7058700</v>
+        <v>7843000</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>22770</v>
+        <v>25300</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15336,14 +15336,14 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>7119360</v>
+        <v>7910400</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>23040</v>
+        <v>25600</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -15468,14 +15468,14 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K237" s="5" t="n">
-        <v>5777280</v>
+        <v>6419200</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>24480</v>
+        <v>27200</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
@@ -15600,14 +15600,14 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>8458200</v>
+        <v>9398000</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>22860</v>
+        <v>25400</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -15662,14 +15662,14 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>8534970</v>
+        <v>9483300</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>23130</v>
+        <v>25700</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -15724,14 +15724,14 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>11403000</v>
+        <v>12670000</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>23130</v>
+        <v>25700</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -15786,14 +15786,14 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>11563560</v>
+        <v>12848400</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>23220</v>
+        <v>25800</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -15848,14 +15848,14 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>14472000</v>
+        <v>16080000</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>25843</v>
+        <v>28714</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
